--- a/suiviexploit/suivi_exploitation_template.xlsx
+++ b/suiviexploit/suivi_exploitation_template.xlsx
@@ -153,6 +153,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="C2:C1000" showErrorMessage="1" errorStyle="stop" errorTitle="Rôle invalide" error="Choisir Dev ou PO dans la liste.">
+      <formula1>"Dev,PO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F2:F1000" showErrorMessage="1" errorStyle="stop" errorTitle="Valeur invalide" error="Choisir Oui ou Non dans la liste.">
+      <formula1>"Oui,Non"</formula1>
+    </dataValidation>
+  </dataValidations>
   <headerFooter/>
 </worksheet>
 </file>
@@ -174,6 +182,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="A2:A1000" showErrorMessage="1" errorStyle="stop" errorTitle="Membre inconnu" error="Choisir un nom présent dans la feuille Membres.">
+      <formula1>Membres!$A$2:$A$1000</formula1>
+    </dataValidation>
+  </dataValidations>
   <headerFooter/>
 </worksheet>
 </file>

--- a/suiviexploit/suivi_exploitation_template.xlsx
+++ b/suiviexploit/suivi_exploitation_template.xlsx
@@ -5,17 +5,39 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Membres" sheetId="1" r:id="rId1"/>
-    <sheet name="Congés" sheetId="2" r:id="rId3"/>
-    <sheet name="Historique" sheetId="3" r:id="rId4"/>
-    <sheet name="Log" sheetId="4" r:id="rId5"/>
+    <sheet name="Parametres" sheetId="1" r:id="rId1"/>
+    <sheet name="Membres" sheetId="2" r:id="rId3"/>
+    <sheet name="Congés" sheetId="3" r:id="rId4"/>
+    <sheet name="Historique" sheetId="4" r:id="rId5"/>
+    <sheet name="Log" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>RolesADesigner</t>
+  </si>
+  <si>
+    <t>Paramètre</t>
+  </si>
+  <si>
+    <t>Valeur</t>
+  </si>
+  <si>
+    <t>Dev</t>
+  </si>
+  <si>
+    <t>EmailsCopieSquad</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
   <si>
     <t>Nom</t>
   </si>
@@ -47,16 +69,7 @@
     <t>SemaineLundi</t>
   </si>
   <si>
-    <t>Dev_Nom</t>
-  </si>
-  <si>
-    <t>Dev_Email</t>
-  </si>
-  <si>
-    <t>PO_Nom</t>
-  </si>
-  <si>
-    <t>PO_Email</t>
+    <t>Role</t>
   </si>
   <si>
     <t>DateAnnonce</t>
@@ -129,35 +142,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="C2:C1000" showErrorMessage="1" errorStyle="stop" errorTitle="Rôle invalide" error="Choisir Dev ou PO dans la liste.">
-      <formula1>"Dev,PO"</formula1>
+    <dataValidation type="list" sqref="C2:C1000" showErrorMessage="1" errorStyle="stop" errorTitle="Rôle invalide" error="Choisir un rôle défini dans la feuille Parametres.">
+      <formula1>Parametres!$A$2:$A$50</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F1000" showErrorMessage="1" errorStyle="stop" errorTitle="Valeur invalide" error="Choisir Oui ou Non dans la liste.">
+    <dataValidation type="list" sqref="F2:F1000" showErrorMessage="1" errorStyle="stop" errorTitle="Valeur invalide" error="Choisir Oui ou Non.">
       <formula1>"Oui,Non"</formula1>
     </dataValidation>
   </dataValidations>
@@ -165,20 +215,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -191,59 +241,56 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/suiviexploit/suivi_exploitation_template.xlsx
+++ b/suiviexploit/suivi_exploitation_template.xlsx
@@ -13,6 +13,49 @@
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <d:author xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">Suivi Exploitation</d:author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Rôles à désigner : un rôle par ligne À PARTIR DE LA LIGNE 2, dans l'ordre d'affichage. 1 rôle = solo, 2 = binôme, 3 = trio, etc. Cette liste alimente la liste déroulante 'Rôle' de la feuille Membres.</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Paramètres self-service (clé en C, valeur en D, dès la ligne 2). Clé reconnue : 'Note &lt;Rôle&gt;' = texte affiché en tête de l'équipe dans le mail d'annonce (ex. 'Note Dev'). IMPORTANT : la config MAIL (From, Subject, Cc, EmailsAdmin) se règle dans 'conf-suivi-squad.json' (dossier de la squad), PAS ici.</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Legacy : copie (Cc) historique. Préférez la clé 'Cc' dans conf-suivi-squad.json, qui a la priorité.</t>
+        </d:r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -174,6 +217,7 @@
     </row>
   </sheetData>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/suiviexploit/suivi_exploitation_template.xlsx
+++ b/suiviexploit/suivi_exploitation_template.xlsx
@@ -43,23 +43,163 @@
         </d:r>
       </text>
     </comment>
-    <comment ref="C2" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">Legacy : copie (Cc) historique. Préférez la clé 'Cc' dans conf-suivi-squad.json, qui a la priorité.</t>
-        </d:r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <d:author xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">Suivi Exploitation</d:author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Une ligne par personne. Nom = identifiant (sert aussi à la feuille Congés et à l'Historique).</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Rôle (liste déroulante = rôles de la feuille Parametres). Une personne = un rôle.</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Compteur : graine de départ (nombre de suivis déjà faits avant la mise en place). NB_FOIS = Compteur + désignations dans l'Historique. Laisser vide (=0) pour un nouveau.</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Actif : Oui/Non. Seuls les 'Oui' sont désignables. Désactiver = mettre Non (ne pas supprimer la ligne).</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">E-mail du membre : destinataire du mail quand la personne est désignée.</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">DateDernierSuivi : informatif uniquement. NON utilisé par l'algorithme (tout est dérivé de l'Historique).</t>
+        </d:r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <d:author xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">Suivi Exploitation</d:author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Début du congé (date). 1 jour = jour entier (pas de demi-journée).</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="A1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Membre en congé (liste déroulante = noms de la feuille Membres).</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Fin du congé (incluse). Un congé chevauchant la semaine cible OU le vendredi précédent exclut la personne.</t>
+        </d:r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <d:author xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">Suivi Exploitation</d:author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">Statut : 'Envoyé' (désignation effective, comptée dans NB_FOIS) ou 'ALERTE' (désignation impossible).</t>
+        </d:r>
+      </text>
+    </comment>
+    <comment ref="A1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">ÉCRIT PAR LE SCRIPT — ne pas saisir à la main. Format long : 1 ligne par rôle désigné et par semaine. SemaineLundi = lundi de la semaine concernée.</t>
+        </d:r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>RolesADesigner</t>
   </si>
@@ -71,12 +211,6 @@
   </si>
   <si>
     <t>Dev</t>
-  </si>
-  <si>
-    <t>EmailsCopieSquad</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>PO</t>
@@ -203,16 +337,10 @@
       <c r="A2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -228,22 +356,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -256,6 +384,7 @@
     </dataValidation>
   </dataValidations>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -266,13 +395,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -282,6 +411,7 @@
     </dataValidation>
   </dataValidations>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -292,32 +422,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -328,13 +459,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/suiviexploit/suivi_exploitation_template.xlsx
+++ b/suiviexploit/suivi_exploitation_template.xlsx
@@ -115,7 +115,7 @@
             <sz val="11"/>
             <rFont val="Calibri"/>
           </rPr>
-          <t xml:space="preserve">DateDernierSuivi : informatif uniquement. NON utilisé par l'algorithme (tout est dérivé de l'Historique).</t>
+          <t xml:space="preserve">DateDernierSuivi = GRAINE de la derniere designation : prise en compte UNIQUEMENT tant que la personne n'a aucune ligne dans l'Historique (sert a initialiser la rotation). Des qu'une designation reelle apparait dans Historique, c'est elle qui prime. Format date jj/MM/aaaa.</t>
         </d:r>
       </text>
     </comment>

--- a/suiviexploit/suivi_exploitation_template.xlsx
+++ b/suiviexploit/suivi_exploitation_template.xlsx
@@ -82,7 +82,7 @@
             <sz val="11"/>
             <rFont val="Calibri"/>
           </rPr>
-          <t xml:space="preserve">Compteur : graine de départ (nombre de suivis déjà faits avant la mise en place). NB_FOIS = Compteur + désignations dans l'Historique. Laisser vide (=0) pour un nouveau.</t>
+          <t xml:space="preserve">Compteur = CUMUL VIVANT du nombre de désignations, écrit par le script à chaque désignation (colonne mise à jour automatiquement). La valeur initiale que tu saisis sert de POINT DE DÉPART (nombre déjà effectué avant la mise en place) ; laisser vide = 0. C'est ce compteur (le moins élevé) qui est utilisé pour la rotation.</t>
         </d:r>
       </text>
     </comment>

--- a/suiviexploit/suivi_exploitation_template.xlsx
+++ b/suiviexploit/suivi_exploitation_template.xlsx
@@ -306,8 +306,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -353,28 +357,37 @@
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9.140625" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9.140625" customWidth="1" style="2"/>
+    <col min="4" max="4" width="9.140625" customWidth="1" style="2"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1" style="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection insertRows="0" deleteRows="0" formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0" sheet="1"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2:C1000" showErrorMessage="1" errorStyle="stop" errorTitle="Rôle invalide" error="Choisir un rôle défini dans la feuille Parametres.">
       <formula1>Parametres!$A$2:$A$50</formula1>
@@ -447,6 +460,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection autoFilter="0" sheet="1"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -469,6 +483,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection autoFilter="0" sheet="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/suiviexploit/suivi_exploitation_template.xlsx
+++ b/suiviexploit/suivi_exploitation_template.xlsx
@@ -306,12 +306,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,37 +353,28 @@
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9.140625" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9.140625" customWidth="1" style="2"/>
-    <col min="4" max="4" width="9.140625" customWidth="1" style="2"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1" style="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection insertRows="0" deleteRows="0" formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0" sheet="1"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2:C1000" showErrorMessage="1" errorStyle="stop" errorTitle="Rôle invalide" error="Choisir un rôle défini dans la feuille Parametres.">
       <formula1>Parametres!$A$2:$A$50</formula1>
@@ -460,7 +447,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection autoFilter="0" sheet="1"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -483,7 +469,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection autoFilter="0" sheet="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/suiviexploit/suivi_exploitation_template.xlsx
+++ b/suiviexploit/suivi_exploitation_template.xlsx
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>RolesADesigner</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Fin</t>
+  </si>
+  <si>
+    <t>Type (vide = journées ; Demi = demi-journées)</t>
   </si>
   <si>
     <t>SemaineLundi</t>
@@ -390,7 +393,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -402,6 +405,9 @@
       </c>
       <c r="C1" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -422,10 +428,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -434,16 +440,16 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -459,13 +465,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
